--- a/docs/so-sanh-domain-trong-nuoc-va-vercel-moi.xlsx
+++ b/docs/so-sanh-domain-trong-nuoc-va-vercel-moi.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04666FAA-DDD5-4993-BF6E-CB2808557952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="1. Tổng quan" sheetId="1" r:id="rId1"/>
@@ -18,13 +17,27 @@
     <sheet name="8. Khuyến nghị" sheetId="8" r:id="rId8"/>
     <sheet name="9. Checklist go-live" sheetId="9" r:id="rId9"/>
     <sheet name="10. Quyết định" sheetId="10" r:id="rId10"/>
+    <sheet name="11. PA2 Thien Duc" sheetId="11" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="328">
   <si>
     <t>SO SÁNH DOMAIN &amp; TRIỂN KHAI — TRONG NƯỚC vs VERCEL</t>
   </si>
@@ -65,19 +78,22 @@
     <t>Tốc độ FE tại VN</t>
   </si>
   <si>
-    <t>Tốt nếu server đặt tại VN</t>
-  </si>
-  <si>
-    <t>Tốt nhờ CDN toàn cầu</t>
+    <t>Tot neu server dat tai VN</t>
+  </si>
+  <si>
+    <t>Tot nho CDN toan cau</t>
   </si>
   <si>
     <t>BE (API + DB)</t>
   </si>
   <si>
-    <t>Tự cài trên VPS: Node.js API + PostgreSQL</t>
-  </si>
-  <si>
-    <t>API serverless trên Vercel; DB thường dịch vụ bên thứ 3</t>
+    <t>Tu cai tren VPS: NestJS API + PostgreSQL</t>
+  </si>
+  <si>
+    <t>PA2: API NestJS tren Render/Railway; FE + Admin tren Vercel</t>
+  </si>
+  <si>
+    <t>Khong dung Vercel Serverless cho NestJS CMS day du</t>
   </si>
   <si>
     <t>Upload ảnh (Cloudinary)</t>
@@ -356,6 +372,9 @@
     <t>Kiểm tra email/mật khẩu, cấp token phiên làm việc</t>
   </si>
   <si>
+    <t>Render/Railway (PA2) - NestJS 24/7</t>
+  </si>
+  <si>
     <t>Phân quyền</t>
   </si>
   <si>
@@ -380,6 +399,9 @@
     <t>PostgreSQL — lưu nội dung + link ảnh</t>
   </si>
   <si>
+    <t>Render Starter ~7-25 USD/thang + DB; Vercel chi host FE + Admin</t>
+  </si>
+  <si>
     <t>Hạng mục BE</t>
   </si>
   <si>
@@ -548,7 +570,7 @@
     <t>Trong nước / Vercel</t>
   </si>
   <si>
-    <t>www.thienduc.com.vn</t>
+    <t>www.thienduc.vn</t>
   </si>
   <si>
     <t>Website chính (FE)</t>
@@ -557,7 +579,7 @@
     <t>VN: IP VPS | Vercel: trỏ Vercel</t>
   </si>
   <si>
-    <t>api.thienduc.com.vn</t>
+    <t>api.thienduc.vn</t>
   </si>
   <si>
     <t>API backend</t>
@@ -566,10 +588,16 @@
     <t>VN: IP VPS | Vercel: Vercel hoặc server riêng</t>
   </si>
   <si>
-    <t>admin.thienduc.com.vn</t>
-  </si>
-  <si>
-    <t>Trang quản trị</t>
+    <t>staging.thienduc.vn</t>
+  </si>
+  <si>
+    <t>Moi truong UAT / kiem thu</t>
+  </si>
+  <si>
+    <t>VN: IP VPS hoac subdomain</t>
+  </si>
+  <si>
+    <t>Vercel: preview hoac subdomain staging</t>
   </si>
   <si>
     <t>CHI PHÍ ƯỚC TÍNH HÀNG NĂM</t>
@@ -722,15 +750,16 @@
     <t>Kiến trúc đề xuất</t>
   </si>
   <si>
-    <t>Tình huống A</t>
-  </si>
-  <si>
-    <t>Ưu tiên ra mắt nhanh, ít vận hành:
-• Domain .com.vn → PA Vietnam / Nhân Hòa
-• FE (Next.js) → Vercel
-• BE (API) → Vercel Serverless hoặc VPS nhỏ VN
-• PostgreSQL → Neon/Supabase (hoặc DB VPS VN nếu cần data in-country)
-• Ảnh → Cloudinary</t>
+    <t>Tinh huong A (PA2 - khuyen nghi Thien Duc)</t>
+  </si>
+  <si>
+    <t>Uu tien ra mat nhanh + CMS day du:
+• Domain .vn / .com.vn → PA Vietnam / Nhan Hoa
+• FE Next.js → thienduc.vn (Vercel)
+• Admin Vite+React → admin.thienduc.vn (Vercel)
+• BE NestJS + PostgreSQL → api.thienduc.vn (Render/Railway)
+• Anh → Cloudinary
+• Staging → staging.thienduc.vn</t>
   </si>
   <si>
     <t>Tình huống B</t>
@@ -906,17 +935,122 @@
   <si>
     <t>Gấp (&lt; 2 tuần) → Vercel | Không gấp + cần hạ tầng VN → VPS VN</t>
   </si>
+  <si>
+    <t>PHUONG AN 2 - ANH XA HOSTING THIEN DUC</t>
+  </si>
+  <si>
+    <t>Thanh phan</t>
+  </si>
+  <si>
+    <t>Cong nghe</t>
+  </si>
+  <si>
+    <t>Hosting de xuat</t>
+  </si>
+  <si>
+    <t>Domain / ghi chu</t>
+  </si>
+  <si>
+    <t>Website cong khai</t>
+  </si>
+  <si>
+    <t>Next.js 16</t>
+  </si>
+  <si>
+    <t>thienduc.vn + www</t>
+  </si>
+  <si>
+    <t>Trang quan tri CMS</t>
+  </si>
+  <si>
+    <t>Vite + React</t>
+  </si>
+  <si>
+    <t>admin.thienduc.vn</t>
+  </si>
+  <si>
+    <t>Backend API</t>
+  </si>
+  <si>
+    <t>NestJS + Prisma</t>
+  </si>
+  <si>
+    <t>Render / Railway</t>
+  </si>
+  <si>
+    <t>api.thienduc.vn - khong dat tren Vercel Serverless</t>
+  </si>
+  <si>
+    <t>Co so du lieu</t>
+  </si>
+  <si>
+    <t>Render / Neon</t>
+  </si>
+  <si>
+    <t>Managed backup</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Cloudinary</t>
+  </si>
+  <si>
+    <t>Cloudinary CDN</t>
+  </si>
+  <si>
+    <t>Upload tu admin</t>
+  </si>
+  <si>
+    <t>Email form</t>
+  </si>
+  <si>
+    <t>Gmail SMTP</t>
+  </si>
+  <si>
+    <t>Google Workspace</t>
+  </si>
+  <si>
+    <t>Thong bao admin</t>
+  </si>
+  <si>
+    <t>Staging</t>
+  </si>
+  <si>
+    <t>Ban build UAT</t>
+  </si>
+  <si>
+    <t>Vercel preview / subdomain</t>
+  </si>
+  <si>
+    <t>Chi phi uoc tinh/thang</t>
+  </si>
+  <si>
+    <t>400k - 1,5 trieu VND</t>
+  </si>
+  <si>
+    <t>Xem sheet 6</t>
+  </si>
+  <si>
+    <t>Free tier co the du giai doan dau</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -924,43 +1058,188 @@
       <sz val="16"/>
       <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF59646A"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFB85450"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF1F4E79"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFB85450"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -970,30 +1249,221 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFB06613"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEEF5FF"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF6EFFF"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF9F9F9"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD5E8D4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1031,73 +1501,359 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1419,185 +2175,183 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+    <row r="1" ht="27.95" customHeight="1" spans="1:4">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-    </row>
-    <row r="2" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-    </row>
-    <row r="4" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" ht="36" customHeight="1" spans="1:4">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="4" ht="21.95" customHeight="1" spans="1:4">
+      <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="5" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+    <row r="6" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row r="7" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A8" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A10" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="2" t="s">
+    <row r="11" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="2" t="s">
+    <row r="12" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A12" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="2" t="s">
+    <row r="13" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="3" t="s">
+    <row r="14" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A14" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="B14" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="C14" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1607,81 +2361,83 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>279</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-    </row>
-    <row r="4" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+    <row r="1" ht="27.95" customHeight="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="4" ht="21.95" customHeight="1" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1" spans="1:4">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="B5" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1" spans="1:4">
+      <c r="A6" s="3">
         <v>2</v>
       </c>
-      <c r="B6" s="15" t="s">
-        <v>284</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="B6" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1" spans="1:4">
+      <c r="A7" s="3">
         <v>3</v>
       </c>
-      <c r="B7" s="15" t="s">
-        <v>286</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="B7" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1" spans="1:4">
+      <c r="A8" s="3">
         <v>4</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>288</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>289</v>
+      <c r="B8" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -1689,137 +2445,282 @@
     <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B5" t="s">
+        <v>307</v>
+      </c>
+      <c r="C5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D5" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>310</v>
+      </c>
+      <c r="B6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" t="s">
+        <v>311</v>
+      </c>
+      <c r="D6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>313</v>
+      </c>
+      <c r="B7" t="s">
+        <v>314</v>
+      </c>
+      <c r="C7" t="s">
+        <v>315</v>
+      </c>
+      <c r="D7" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>317</v>
+      </c>
+      <c r="B8" t="s">
+        <v>318</v>
+      </c>
+      <c r="C8" t="s">
+        <v>319</v>
+      </c>
+      <c r="D8" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>321</v>
+      </c>
+      <c r="B9" t="s">
+        <v>322</v>
+      </c>
+      <c r="C9" t="s">
+        <v>323</v>
+      </c>
+      <c r="D9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>324</v>
+      </c>
+      <c r="B10" t="s">
+        <v>325</v>
+      </c>
+      <c r="C10" t="s">
+        <v>326</v>
+      </c>
+      <c r="D10" t="s">
+        <v>327</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-    </row>
-    <row r="2" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+    <row r="1" ht="27.95" customHeight="1" spans="1:4">
+      <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-    </row>
-    <row r="4" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" ht="36" customHeight="1" spans="1:4">
+      <c r="A2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="4" ht="21.95" customHeight="1" spans="1:4">
+      <c r="A4" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="2" t="s">
+    </row>
+    <row r="5" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A5" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="2" t="s">
+    </row>
+    <row r="6" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A6" s="13" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="2" t="s">
+    </row>
+    <row r="7" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A7" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="2" t="s">
+    </row>
+    <row r="8" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A8" s="13" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="2" t="s">
+    </row>
+    <row r="9" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A9" s="3" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="2" t="s">
+    </row>
+    <row r="10" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A10" s="13" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="2" t="s">
+    </row>
+    <row r="11" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A11" s="3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="2" t="s">
+    </row>
+    <row r="12" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A12" s="13" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="2" t="s">
+    </row>
+    <row r="13" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A13" s="3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="2" t="s">
+    </row>
+    <row r="14" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A14" s="13" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="2" t="s">
+    </row>
+    <row r="15" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A15" s="3" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="2" t="s">
+    </row>
+    <row r="16" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A16" s="13" t="s">
         <v>64</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1828,181 +2729,183 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-    </row>
-    <row r="2" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+    <row r="1" ht="27.95" customHeight="1" spans="1:4">
+      <c r="A1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-    </row>
-    <row r="4" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" ht="36" customHeight="1" spans="1:4">
+      <c r="A2" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="4" ht="21.95" customHeight="1" spans="1:4">
+      <c r="A4" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="B4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="5" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A6" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A8" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A10" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A11" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" ht="15.6" spans="1:4">
+      <c r="A13" s="19" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" ht="21.95" customHeight="1" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B15" s="3" t="s">
+    <row r="15" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A15" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="B15" s="16" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="C15" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="B16" s="3" t="s">
+    </row>
+    <row r="16" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A16" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="B16" s="16" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="C16" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="B17" s="3" t="s">
+    </row>
+    <row r="17" ht="39.95" customHeight="1" spans="1:3">
+      <c r="A17" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="B17" s="16" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="C17" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="B18" s="3" t="s">
+    </row>
+    <row r="18" ht="39.95" customHeight="1" spans="1:3">
+      <c r="A18" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="B18" s="16" t="s">
         <v>103</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -2011,176 +2914,183 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-    </row>
-    <row r="2" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+    <row r="1" ht="27.95" customHeight="1" spans="1:4">
+      <c r="A1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-    </row>
-    <row r="4" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" ht="36" customHeight="1" spans="1:4">
+      <c r="A2" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="4" ht="21.95" customHeight="1" spans="1:4">
+      <c r="A4" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="B4" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B5" s="2" t="s">
+    <row r="5" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A5" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="B5" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A6" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" s="2" t="s">
+    <row r="7" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A7" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C7" s="2" t="s">
+    <row r="8" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A8" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C8" s="2" t="s">
+    <row r="9" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A9" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" s="1" t="s">
+    <row r="10" spans="1:4">
+      <c r="C10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" ht="21.95" customHeight="1" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+    <row r="12" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A12" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B12" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C12" s="17" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    <row r="13" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A13" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B13" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C13" s="17" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+    <row r="14" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A14" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B14" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C14" s="17" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+    <row r="15" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A15" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B15" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C15" s="17" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+    <row r="16" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A16" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B16" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C16" s="17" t="s">
         <v>136</v>
+      </c>
+    </row>
+    <row r="17" ht="39.95" customHeight="1" spans="1:3">
+      <c r="A17" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2189,203 +3099,208 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="3" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-    </row>
-    <row r="2" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-    </row>
-    <row r="4" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="1" ht="27.95" customHeight="1" spans="1:4">
+      <c r="A1" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" ht="36" customHeight="1" spans="1:4">
+      <c r="A2" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="4" ht="21.95" customHeight="1" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+    <row r="5" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A5" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B5" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C5" s="17" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row r="6" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A6" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B6" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C6" s="17" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+    <row r="7" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A7" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B7" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C7" s="17" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+    <row r="8" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A8" s="13" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="B8" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C8" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="C11" s="1" t="s">
+    </row>
+    <row r="10" ht="15.6" spans="1:4">
+      <c r="A10" s="19" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" ht="21.95" customHeight="1" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+    <row r="12" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A12" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B12" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C12" s="17" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    <row r="13" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A13" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B13" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C13" s="17" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+    <row r="14" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A14" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B14" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C14" s="17" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+    <row r="15" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A15" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B15" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C15" s="17" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+    <row r="16" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A16" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B16" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C16" s="17" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+    <row r="18" ht="21.95" customHeight="1" spans="1:4">
+      <c r="A18" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C18" s="2" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+    <row r="19" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A19" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B19" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C19" s="17" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+    <row r="20" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A20" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B20" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>176</v>
+      <c r="C20" s="17" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="21" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A21" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="D21" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -2394,121 +3309,123 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="3" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-    </row>
-    <row r="2" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-    </row>
-    <row r="4" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" s="1" t="s">
+    <row r="1" ht="27.95" customHeight="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" ht="36" customHeight="1" spans="1:4">
+      <c r="A2" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="4" ht="21.95" customHeight="1" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C6" s="4" t="s">
+    <row r="5" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A5" s="3" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="B5" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C5" s="17" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+    <row r="6" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A6" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B6" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C6" s="17" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    <row r="7" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A7" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C7" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="C9" s="4" t="s">
+    </row>
+    <row r="8" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A8" s="13" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="B8" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C8" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="C10" s="4" t="s">
+    </row>
+    <row r="9" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A9" s="3" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="B9" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="C9" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="C11" s="7" t="s">
+    </row>
+    <row r="10" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A10" s="13" t="s">
         <v>204</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="11" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A11" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -2517,132 +3434,134 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="2" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-    </row>
-    <row r="2" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
-        <v>206</v>
-      </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="B4" s="18"/>
-    </row>
-    <row r="5" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+    <row r="1" ht="27.95" customHeight="1" spans="1:4">
+      <c r="A1" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" ht="36" customHeight="1" spans="1:4">
+      <c r="A2" s="5" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="4" ht="15.6" spans="1:4">
+      <c r="A4" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B4" s="14"/>
+    </row>
+    <row r="5" ht="21.95" customHeight="1" spans="1:4">
+      <c r="A5" s="2" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B8" s="2" t="s">
+    </row>
+    <row r="6" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A6" s="3" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B9" s="2" t="s">
+    </row>
+    <row r="7" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A7" s="13" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="B7" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B11" s="19"/>
-    </row>
-    <row r="12" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+    </row>
+    <row r="8" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A8" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+    <row r="9" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A9" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+    <row r="11" ht="15.6" spans="1:4">
+      <c r="A11" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B11" s="15"/>
+    </row>
+    <row r="12" ht="21.95" customHeight="1" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="13" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A13" s="3" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="B16" s="2" t="s">
+    </row>
+    <row r="14" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A14" s="13" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B17" s="2" t="s">
+    </row>
+    <row r="15" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A15" s="3" t="s">
         <v>228</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="16" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A16" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="17" ht="39.95" customHeight="1" spans="1:2">
+      <c r="A17" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -2653,94 +3572,96 @@
     <mergeCell ref="A11:B11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="78" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-    </row>
-    <row r="3" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+    <row r="1" ht="27.95" customHeight="1" spans="1:4">
+      <c r="A1" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="3" ht="21.95" customHeight="1" spans="1:4">
+      <c r="A3" s="2" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="B3" s="2" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+    <row r="4" ht="99.95" customHeight="1" spans="1:4">
+      <c r="A4" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B4" s="10" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    <row r="5" ht="99.95" customHeight="1" spans="1:4">
+      <c r="A5" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B5" s="10" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+    <row r="7" ht="15.6" spans="1:4">
+      <c r="A7" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="B10" s="2" t="s">
+    </row>
+    <row r="8" ht="21.95" customHeight="1" spans="1:4">
+      <c r="A8" s="2" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B11" s="2" t="s">
+    </row>
+    <row r="9" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A9" s="3" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B12" s="2" t="s">
+    </row>
+    <row r="10" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A10" s="13" t="s">
         <v>246</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="11" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A11" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="12" ht="39.95" customHeight="1" spans="1:4">
+      <c r="A12" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -2748,14 +3669,16 @@
     <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -2763,240 +3686,240 @@
     <col min="5" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>247</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-    </row>
-    <row r="2" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
-        <v>248</v>
-      </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-    </row>
-    <row r="4" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" s="1" t="s">
+    <row r="1" ht="27.95" customHeight="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" ht="36" customHeight="1" spans="1:6">
+      <c r="A2" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="4" ht="21.95" customHeight="1" spans="1:6">
+      <c r="A4" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
+      <c r="E4" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="5" ht="32.1" customHeight="1" spans="1:6">
+      <c r="A5" s="6">
         <v>1</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12">
+      <c r="B5" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="6" ht="32.1" customHeight="1" spans="1:6">
+      <c r="A6" s="6">
         <v>2</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12">
+      <c r="B6" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="7" ht="32.1" customHeight="1" spans="1:6">
+      <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="C7" s="13" t="s">
+      <c r="B7" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D7" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12">
+      <c r="F7" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="8" ht="32.1" customHeight="1" spans="1:6">
+      <c r="A8" s="6">
         <v>4</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="12">
+      <c r="B8" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="9" ht="32.1" customHeight="1" spans="1:6">
+      <c r="A9" s="6">
         <v>5</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>264</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>266</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12">
+      <c r="B9" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="10" ht="32.1" customHeight="1" spans="1:6">
+      <c r="A10" s="6">
         <v>6</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
+      <c r="B10" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="11" ht="32.1" customHeight="1" spans="1:6">
+      <c r="A11" s="6">
         <v>7</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>269</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12">
+      <c r="B11" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="12" ht="32.1" customHeight="1" spans="1:6">
+      <c r="A12" s="6">
         <v>8</v>
       </c>
-      <c r="B12" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>273</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12">
+      <c r="B12" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="13" ht="32.1" customHeight="1" spans="1:6">
+      <c r="A13" s="6">
         <v>9</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>276</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12">
+      <c r="B13" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="14" ht="32.1" customHeight="1" spans="1:6">
+      <c r="A14" s="6">
         <v>10</v>
       </c>
-      <c r="B14" s="12" t="s">
-        <v>277</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>278</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>254</v>
+      <c r="B14" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -3005,6 +3928,7 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>